--- a/app/src/main/res/raw/member_enu_form.xlsx
+++ b/app/src/main/res/raw/member_enu_form.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27795" windowHeight="12195" tabRatio="500"/>
+    <workbookView windowWidth="24090" windowHeight="11400" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="columns" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="226">
   <si>
     <t>group</t>
   </si>
@@ -843,6 +843,9 @@
     <t xml:space="preserve">አያውቅም  </t>
   </si>
   <si>
+    <t>LOADED_EXTERNALLY</t>
+  </si>
+  <si>
     <t>form_id</t>
   </si>
   <si>
@@ -878,12 +881,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="28">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -902,6 +905,12 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial [Mono]"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -917,17 +926,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Arial"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF800080"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -941,10 +949,18 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -956,11 +972,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color theme="0"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -972,18 +987,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color theme="3"/>
       <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -996,21 +1004,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF3F3F76"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="1"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1018,20 +1020,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1046,7 +1034,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF006100"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1055,6 +1050,20 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1105,7 +1114,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1117,19 +1204,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1141,145 +1282,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1368,17 +1377,6 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
@@ -1397,6 +1395,32 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1425,21 +1449,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -1457,152 +1466,152 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="5" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="11" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="12" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1624,6 +1633,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1675,7 +1688,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -2057,7 +2070,7 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="27" t="s">
+      <c r="J1" s="29" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="1" t="s">
@@ -2075,7 +2088,7 @@
       <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="40" t="s">
+      <c r="P1" s="42" t="s">
         <v>15</v>
       </c>
       <c r="Q1" s="1" t="s">
@@ -2091,15 +2104,15 @@
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="12" t="s">
         <v>20</v>
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-      <c r="H2" s="10" t="s">
+      <c r="H2" s="12" t="s">
         <v>21</v>
       </c>
       <c r="I2" t="s">
@@ -2108,7 +2121,7 @@
       <c r="J2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="K2" s="10" t="s">
+      <c r="K2" s="12" t="s">
         <v>24</v>
       </c>
       <c r="L2" s="1"/>
@@ -2119,7 +2132,7 @@
       <c r="O2" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="P2" s="40"/>
+      <c r="P2" s="42"/>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="1" t="s">
@@ -2140,11 +2153,11 @@
       <c r="J3" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="K3" s="28" t="s">
+      <c r="K3" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="L3" s="29"/>
-      <c r="M3" s="29"/>
+      <c r="L3" s="31"/>
+      <c r="M3" s="31"/>
       <c r="N3" t="b">
         <v>1</v>
       </c>
@@ -2171,11 +2184,11 @@
       <c r="J4" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="K4" s="28" t="s">
+      <c r="K4" s="30" t="s">
         <v>35</v>
       </c>
-      <c r="L4" s="29"/>
-      <c r="M4" s="29"/>
+      <c r="L4" s="31"/>
+      <c r="M4" s="31"/>
       <c r="N4" t="b">
         <v>1</v>
       </c>
@@ -2202,11 +2215,11 @@
       <c r="J5" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="K5" s="28" t="s">
+      <c r="K5" s="30" t="s">
         <v>40</v>
       </c>
-      <c r="L5" s="29"/>
-      <c r="M5" s="29"/>
+      <c r="L5" s="31"/>
+      <c r="M5" s="31"/>
       <c r="N5" t="b">
         <v>1</v>
       </c>
@@ -2233,11 +2246,11 @@
       <c r="J6" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="K6" s="28" t="s">
+      <c r="K6" s="30" t="s">
         <v>46</v>
       </c>
-      <c r="L6" s="29"/>
-      <c r="M6" s="29"/>
+      <c r="L6" s="31"/>
+      <c r="M6" s="31"/>
       <c r="N6" t="b">
         <v>1</v>
       </c>
@@ -2266,11 +2279,11 @@
       <c r="J7" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="K7" s="28" t="s">
+      <c r="K7" s="30" t="s">
         <v>51</v>
       </c>
-      <c r="L7" s="29"/>
-      <c r="M7" s="29"/>
+      <c r="L7" s="31"/>
+      <c r="M7" s="31"/>
       <c r="N7" t="b">
         <v>1</v>
       </c>
@@ -2297,11 +2310,11 @@
       <c r="J8" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="K8" s="28" t="s">
+      <c r="K8" s="30" t="s">
         <v>56</v>
       </c>
-      <c r="L8" s="29"/>
-      <c r="M8" s="29"/>
+      <c r="L8" s="31"/>
+      <c r="M8" s="31"/>
       <c r="N8" t="b">
         <v>1</v>
       </c>
@@ -2328,11 +2341,11 @@
       <c r="J9" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="K9" s="28" t="s">
+      <c r="K9" s="30" t="s">
         <v>61</v>
       </c>
-      <c r="L9" s="29"/>
-      <c r="M9" s="29"/>
+      <c r="L9" s="31"/>
+      <c r="M9" s="31"/>
       <c r="N9" t="b">
         <v>1</v>
       </c>
@@ -2356,11 +2369,11 @@
       <c r="J10" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="K10" s="28" t="s">
+      <c r="K10" s="30" t="s">
         <v>65</v>
       </c>
-      <c r="L10" s="29"/>
-      <c r="M10" s="29"/>
+      <c r="L10" s="31"/>
+      <c r="M10" s="31"/>
       <c r="N10" t="b">
         <v>1</v>
       </c>
@@ -2384,11 +2397,11 @@
       <c r="J11" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="K11" s="28" t="s">
+      <c r="K11" s="30" t="s">
         <v>72</v>
       </c>
-      <c r="L11" s="29"/>
-      <c r="M11" s="29"/>
+      <c r="L11" s="31"/>
+      <c r="M11" s="31"/>
       <c r="N11" t="b">
         <v>1</v>
       </c>
@@ -2410,11 +2423,11 @@
       <c r="J12" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="K12" s="28" t="s">
+      <c r="K12" s="30" t="s">
         <v>78</v>
       </c>
-      <c r="L12" s="29"/>
-      <c r="M12" s="29"/>
+      <c r="L12" s="31"/>
+      <c r="M12" s="31"/>
       <c r="N12" t="b">
         <v>1</v>
       </c>
@@ -2439,15 +2452,15 @@
       <c r="J13" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="K13" s="28" t="s">
+      <c r="K13" s="30" t="s">
         <v>84</v>
       </c>
-      <c r="L13" s="29"/>
-      <c r="M13" s="29"/>
+      <c r="L13" s="31"/>
+      <c r="M13" s="31"/>
       <c r="N13" t="b">
         <v>1</v>
       </c>
-      <c r="P13" s="41" t="s">
+      <c r="P13" s="43" t="s">
         <v>85</v>
       </c>
     </row>
@@ -2468,384 +2481,384 @@
       <c r="J14" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="K14" s="28" t="s">
+      <c r="K14" s="30" t="s">
         <v>90</v>
       </c>
-      <c r="L14" s="29"/>
-      <c r="M14" s="29"/>
+      <c r="L14" s="31"/>
+      <c r="M14" s="31"/>
       <c r="N14" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:18">
-      <c r="A15" s="20"/>
-      <c r="B15" s="18"/>
-      <c r="C15" s="18"/>
-      <c r="D15" s="18" t="s">
+      <c r="A15" s="22"/>
+      <c r="B15" s="20"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20" t="s">
         <v>91</v>
       </c>
-      <c r="E15" s="18" t="s">
+      <c r="E15" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="F15" s="18" t="s">
+      <c r="F15" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="G15" s="18"/>
-      <c r="H15" s="18" t="s">
+      <c r="G15" s="20"/>
+      <c r="H15" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="I15" s="18" t="s">
+      <c r="I15" s="20" t="s">
         <v>94</v>
       </c>
-      <c r="J15" s="18" t="s">
+      <c r="J15" s="20" t="s">
         <v>95</v>
       </c>
-      <c r="K15" s="30" t="s">
+      <c r="K15" s="32" t="s">
         <v>96</v>
       </c>
-      <c r="L15" s="31"/>
-      <c r="M15" s="31"/>
-      <c r="N15" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="O15" s="18"/>
-      <c r="P15" s="18" t="s">
+      <c r="L15" s="33"/>
+      <c r="M15" s="33"/>
+      <c r="N15" s="20" t="b">
+        <v>1</v>
+      </c>
+      <c r="O15" s="20"/>
+      <c r="P15" s="20" t="s">
         <v>97</v>
       </c>
-      <c r="Q15" s="18"/>
-      <c r="R15" s="18"/>
+      <c r="Q15" s="20"/>
+      <c r="R15" s="20"/>
     </row>
     <row r="16" spans="1:18">
-      <c r="A16" s="20"/>
-      <c r="B16" s="18"/>
-      <c r="C16" s="18"/>
-      <c r="D16" s="18" t="s">
+      <c r="A16" s="22"/>
+      <c r="B16" s="20"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="20" t="s">
         <v>98</v>
       </c>
-      <c r="E16" s="18" t="s">
+      <c r="E16" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="F16" s="18" t="s">
+      <c r="F16" s="20" t="s">
         <v>99</v>
       </c>
-      <c r="G16" s="18"/>
-      <c r="H16" s="18" t="s">
+      <c r="G16" s="20"/>
+      <c r="H16" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="I16" s="18" t="s">
+      <c r="I16" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="J16" s="18" t="s">
+      <c r="J16" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="K16" s="30" t="s">
+      <c r="K16" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="L16" s="31"/>
-      <c r="M16" s="31"/>
-      <c r="N16" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="O16" s="18"/>
-      <c r="P16" s="18"/>
-      <c r="Q16" s="18"/>
-      <c r="R16" s="18"/>
-    </row>
-    <row r="17" s="16" customFormat="1" spans="1:14">
-      <c r="A17" s="21"/>
-      <c r="D17" s="16" t="s">
+      <c r="L16" s="33"/>
+      <c r="M16" s="33"/>
+      <c r="N16" s="20" t="b">
+        <v>1</v>
+      </c>
+      <c r="O16" s="20"/>
+      <c r="P16" s="20"/>
+      <c r="Q16" s="20"/>
+      <c r="R16" s="20"/>
+    </row>
+    <row r="17" s="18" customFormat="1" spans="1:14">
+      <c r="A17" s="23"/>
+      <c r="D17" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="E17" s="16" t="s">
+      <c r="E17" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="F17" s="16" t="s">
+      <c r="F17" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="H17" s="16" t="s">
+      <c r="H17" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="I17" s="32" t="s">
+      <c r="I17" s="34" t="s">
         <v>106</v>
       </c>
-      <c r="J17" s="32" t="s">
+      <c r="J17" s="34" t="s">
         <v>107</v>
       </c>
-      <c r="K17" s="33" t="s">
+      <c r="K17" s="35" t="s">
         <v>108</v>
       </c>
-      <c r="L17" s="34"/>
-      <c r="M17" s="34"/>
-      <c r="N17" s="16" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" s="16" customFormat="1" spans="1:17">
-      <c r="A18" s="21"/>
-      <c r="D18" s="16" t="s">
+      <c r="L17" s="36"/>
+      <c r="M17" s="36"/>
+      <c r="N17" s="18" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" s="18" customFormat="1" spans="1:17">
+      <c r="A18" s="23"/>
+      <c r="D18" s="18" t="s">
         <v>109</v>
       </c>
-      <c r="E18" s="16" t="s">
+      <c r="E18" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="H18" s="16" t="s">
+      <c r="H18" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="I18" s="32" t="s">
+      <c r="I18" s="34" t="s">
         <v>111</v>
       </c>
-      <c r="J18" s="32" t="s">
+      <c r="J18" s="34" t="s">
         <v>112</v>
       </c>
-      <c r="K18" s="33" t="s">
+      <c r="K18" s="35" t="s">
         <v>113</v>
       </c>
-      <c r="L18" s="34"/>
-      <c r="M18" s="34"/>
-      <c r="N18" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="P18" s="16" t="s">
+      <c r="L18" s="36"/>
+      <c r="M18" s="36"/>
+      <c r="N18" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="P18" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="Q18" s="16" t="s">
+      <c r="Q18" s="18" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="19" s="16" customFormat="1" spans="1:17">
-      <c r="A19" s="21"/>
-      <c r="D19" s="16" t="s">
+    <row r="19" s="18" customFormat="1" spans="1:17">
+      <c r="A19" s="23"/>
+      <c r="D19" s="18" t="s">
         <v>116</v>
       </c>
-      <c r="E19" s="16" t="s">
+      <c r="E19" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="H19" s="25" t="s">
+      <c r="H19" s="27" t="s">
         <v>117</v>
       </c>
-      <c r="I19" s="32" t="s">
+      <c r="I19" s="34" t="s">
         <v>118</v>
       </c>
-      <c r="J19" s="32" t="s">
+      <c r="J19" s="34" t="s">
         <v>119</v>
       </c>
-      <c r="K19" s="33" t="s">
+      <c r="K19" s="35" t="s">
         <v>120</v>
       </c>
-      <c r="L19" s="34"/>
-      <c r="M19" s="34"/>
-      <c r="P19" s="16" t="s">
+      <c r="L19" s="36"/>
+      <c r="M19" s="36"/>
+      <c r="P19" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="Q19" s="16" t="s">
+      <c r="Q19" s="18" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="20" s="17" customFormat="1" spans="1:15">
-      <c r="A20" s="22" t="s">
+    <row r="20" s="19" customFormat="1" spans="1:15">
+      <c r="A20" s="24" t="s">
         <v>121</v>
       </c>
-      <c r="D20" s="17" t="s">
+      <c r="D20" s="19" t="s">
         <v>122</v>
       </c>
-      <c r="E20" s="17" t="s">
+      <c r="E20" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="F20" s="26"/>
-      <c r="G20" s="26"/>
-      <c r="H20" s="17" t="s">
+      <c r="F20" s="28"/>
+      <c r="G20" s="28"/>
+      <c r="H20" s="19" t="s">
         <v>124</v>
       </c>
-      <c r="I20" s="17" t="s">
+      <c r="I20" s="19" t="s">
         <v>125</v>
       </c>
-      <c r="J20" s="17" t="s">
+      <c r="J20" s="19" t="s">
         <v>126</v>
       </c>
-      <c r="K20" s="35" t="s">
+      <c r="K20" s="37" t="s">
         <v>127</v>
       </c>
-      <c r="L20" s="36"/>
-      <c r="M20" s="36"/>
-      <c r="N20" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="O20" s="17" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" s="18" customFormat="1" spans="1:15">
-      <c r="A21" s="23" t="s">
+      <c r="L20" s="38"/>
+      <c r="M20" s="38"/>
+      <c r="N20" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="O20" s="19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" s="20" customFormat="1" spans="1:15">
+      <c r="A21" s="25" t="s">
         <v>121</v>
       </c>
-      <c r="D21" s="18" t="s">
+      <c r="D21" s="20" t="s">
         <v>128</v>
       </c>
-      <c r="E21" s="18" t="s">
+      <c r="E21" s="20" t="s">
         <v>129</v>
       </c>
-      <c r="H21" s="18" t="s">
+      <c r="H21" s="20" t="s">
         <v>130</v>
       </c>
-      <c r="I21" s="18" t="s">
+      <c r="I21" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="J21" s="37" t="s">
+      <c r="J21" s="39" t="s">
         <v>132</v>
       </c>
-      <c r="K21" s="30" t="s">
+      <c r="K21" s="32" t="s">
         <v>133</v>
       </c>
-      <c r="L21" s="31"/>
-      <c r="M21" s="31"/>
-      <c r="N21" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="O21" s="18" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" s="18" customFormat="1" spans="1:18">
-      <c r="A22" s="23" t="s">
+      <c r="L21" s="33"/>
+      <c r="M21" s="33"/>
+      <c r="N21" s="20" t="b">
+        <v>1</v>
+      </c>
+      <c r="O21" s="20" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" s="20" customFormat="1" spans="1:18">
+      <c r="A22" s="25" t="s">
         <v>121</v>
       </c>
-      <c r="D22" s="18" t="s">
+      <c r="D22" s="20" t="s">
         <v>134</v>
       </c>
-      <c r="E22" s="18" t="s">
+      <c r="E22" s="20" t="s">
         <v>135</v>
       </c>
-      <c r="F22" s="20"/>
-      <c r="G22" s="20"/>
-      <c r="H22" s="18" t="s">
+      <c r="F22" s="22"/>
+      <c r="G22" s="22"/>
+      <c r="H22" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="I22" s="18" t="s">
+      <c r="I22" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="J22" s="37" t="s">
+      <c r="J22" s="39" t="s">
         <v>136</v>
       </c>
-      <c r="K22" s="30" t="s">
+      <c r="K22" s="32" t="s">
         <v>137</v>
       </c>
-      <c r="L22" s="31"/>
-      <c r="M22" s="31"/>
-      <c r="O22" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="R22" s="18" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" s="18" customFormat="1" spans="1:18">
-      <c r="A23" s="23" t="s">
+      <c r="L22" s="33"/>
+      <c r="M22" s="33"/>
+      <c r="O22" s="20" t="b">
+        <v>1</v>
+      </c>
+      <c r="R22" s="20" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" s="20" customFormat="1" spans="1:18">
+      <c r="A23" s="25" t="s">
         <v>121</v>
       </c>
-      <c r="D23" s="18" t="s">
+      <c r="D23" s="20" t="s">
         <v>138</v>
       </c>
-      <c r="E23" s="18" t="s">
+      <c r="E23" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="F23" s="20"/>
-      <c r="G23" s="20"/>
-      <c r="H23" s="18" t="s">
+      <c r="F23" s="22"/>
+      <c r="G23" s="22"/>
+      <c r="H23" s="20" t="s">
         <v>139</v>
       </c>
-      <c r="I23" s="18" t="s">
+      <c r="I23" s="20" t="s">
         <v>139</v>
       </c>
-      <c r="J23" s="37" t="s">
+      <c r="J23" s="39" t="s">
         <v>139</v>
       </c>
-      <c r="K23" s="30" t="s">
+      <c r="K23" s="32" t="s">
         <v>140</v>
       </c>
-      <c r="L23" s="31"/>
-      <c r="M23" s="31"/>
-      <c r="O23" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="R23" s="18" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" s="18" customFormat="1" spans="1:18">
-      <c r="A24" s="23" t="s">
+      <c r="L23" s="33"/>
+      <c r="M23" s="33"/>
+      <c r="O23" s="20" t="b">
+        <v>1</v>
+      </c>
+      <c r="R23" s="20" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" s="20" customFormat="1" spans="1:18">
+      <c r="A24" s="25" t="s">
         <v>121</v>
       </c>
-      <c r="D24" s="18" t="s">
+      <c r="D24" s="20" t="s">
         <v>141</v>
       </c>
-      <c r="E24" s="18" t="s">
+      <c r="E24" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="F24" s="20"/>
-      <c r="G24" s="20"/>
-      <c r="H24" s="18" t="s">
+      <c r="F24" s="22"/>
+      <c r="G24" s="22"/>
+      <c r="H24" s="20" t="s">
         <v>142</v>
       </c>
-      <c r="I24" s="18" t="s">
+      <c r="I24" s="20" t="s">
         <v>142</v>
       </c>
-      <c r="J24" s="37" t="s">
+      <c r="J24" s="39" t="s">
         <v>142</v>
       </c>
-      <c r="K24" s="30" t="s">
+      <c r="K24" s="32" t="s">
         <v>143</v>
       </c>
-      <c r="L24" s="31"/>
-      <c r="M24" s="31"/>
-      <c r="O24" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="R24" s="18" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" s="19" customFormat="1" spans="1:15">
-      <c r="A25" s="24" t="s">
+      <c r="L24" s="33"/>
+      <c r="M24" s="33"/>
+      <c r="O24" s="20" t="b">
+        <v>1</v>
+      </c>
+      <c r="R24" s="20" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" s="21" customFormat="1" spans="1:15">
+      <c r="A25" s="26" t="s">
         <v>121</v>
       </c>
-      <c r="D25" s="19" t="s">
+      <c r="D25" s="21" t="s">
         <v>144</v>
       </c>
-      <c r="E25" s="19" t="s">
+      <c r="E25" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="H25" s="19" t="s">
+      <c r="H25" s="21" t="s">
         <v>145</v>
       </c>
-      <c r="I25" s="19" t="s">
+      <c r="I25" s="21" t="s">
         <v>146</v>
       </c>
-      <c r="J25" s="19" t="s">
+      <c r="J25" s="21" t="s">
         <v>147</v>
       </c>
-      <c r="K25" s="38" t="s">
+      <c r="K25" s="40" t="s">
         <v>148</v>
       </c>
-      <c r="L25" s="39"/>
-      <c r="M25" s="39"/>
-      <c r="N25" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="O25" s="19" t="b">
+      <c r="L25" s="41"/>
+      <c r="M25" s="41"/>
+      <c r="N25" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="O25" s="21" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:13">
       <c r="A26" s="1"/>
-      <c r="K26" s="29"/>
-      <c r="L26" s="29"/>
-      <c r="M26" s="29"/>
+      <c r="K26" s="31"/>
+      <c r="L26" s="31"/>
+      <c r="M26" s="31"/>
     </row>
     <row r="27" spans="1:13">
       <c r="A27" s="1"/>
-      <c r="K27" s="29"/>
-      <c r="L27" s="29"/>
-      <c r="M27" s="29"/>
+      <c r="K27" s="31"/>
+      <c r="L27" s="31"/>
+      <c r="M27" s="31"/>
     </row>
     <row r="28" spans="1:13">
       <c r="A28" s="1"/>
@@ -2899,7 +2912,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultColWidth="9.18095238095238" defaultRowHeight="12.75" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="12.5428571428571" customWidth="1"/>
@@ -2947,10 +2960,10 @@
       <c r="D2" t="s">
         <v>152</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="11" t="s">
         <v>153</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="F2" s="12" t="s">
         <v>154</v>
       </c>
     </row>
@@ -2967,10 +2980,10 @@
       <c r="D3" t="s">
         <v>157</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="F3" s="12" t="s">
         <v>159</v>
       </c>
     </row>
@@ -2987,10 +3000,10 @@
       <c r="D4" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="13" t="s">
         <v>163</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="F4" s="14" t="s">
         <v>164</v>
       </c>
       <c r="G4" s="4"/>
@@ -3008,10 +3021,10 @@
       <c r="D5" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="E5" s="13" t="s">
         <v>168</v>
       </c>
-      <c r="F5" s="12" t="s">
+      <c r="F5" s="14" t="s">
         <v>169</v>
       </c>
       <c r="G5" s="4"/>
@@ -3029,13 +3042,13 @@
       <c r="D6" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="E6" s="13" t="s">
         <v>173</v>
       </c>
-      <c r="F6" s="13" t="s">
+      <c r="F6" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="G6" s="14" t="s">
+      <c r="G6" s="16" t="s">
         <v>150</v>
       </c>
     </row>
@@ -3052,10 +3065,10 @@
       <c r="D7" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="E7" s="15" t="s">
+      <c r="E7" s="17" t="s">
         <v>178</v>
       </c>
-      <c r="F7" s="10" t="s">
+      <c r="F7" s="12" t="s">
         <v>179</v>
       </c>
     </row>
@@ -3072,10 +3085,10 @@
       <c r="D8" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="E8" s="15" t="s">
+      <c r="E8" s="17" t="s">
         <v>183</v>
       </c>
-      <c r="F8" s="10" t="s">
+      <c r="F8" s="12" t="s">
         <v>184</v>
       </c>
     </row>
@@ -3092,10 +3105,10 @@
       <c r="D9" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="E9" s="15" t="s">
+      <c r="E9" s="17" t="s">
         <v>188</v>
       </c>
-      <c r="F9" s="10" t="s">
+      <c r="F9" s="12" t="s">
         <v>189</v>
       </c>
     </row>
@@ -3112,10 +3125,10 @@
       <c r="D10" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="E10" s="15" t="s">
+      <c r="E10" s="17" t="s">
         <v>193</v>
       </c>
-      <c r="F10" s="10" t="s">
+      <c r="F10" s="12" t="s">
         <v>194</v>
       </c>
     </row>
@@ -3132,10 +3145,10 @@
       <c r="D11" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="E11" s="15" t="s">
+      <c r="E11" s="17" t="s">
         <v>198</v>
       </c>
-      <c r="F11" s="10" t="s">
+      <c r="F11" s="12" t="s">
         <v>199</v>
       </c>
     </row>
@@ -3152,10 +3165,10 @@
       <c r="D12" s="8" t="s">
         <v>202</v>
       </c>
-      <c r="E12" s="15" t="s">
+      <c r="E12" s="17" t="s">
         <v>203</v>
       </c>
-      <c r="F12" s="10" t="s">
+      <c r="F12" s="12" t="s">
         <v>204</v>
       </c>
     </row>
@@ -3172,10 +3185,10 @@
       <c r="D13" s="8" t="s">
         <v>207</v>
       </c>
-      <c r="E13" s="15" t="s">
+      <c r="E13" s="17" t="s">
         <v>208</v>
       </c>
-      <c r="F13" s="10" t="s">
+      <c r="F13" s="12" t="s">
         <v>209</v>
       </c>
     </row>
@@ -3192,11 +3205,51 @@
       <c r="D14" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="E14" s="15" t="s">
+      <c r="E14" s="17" t="s">
         <v>213</v>
       </c>
-      <c r="F14" s="10" t="s">
+      <c r="F14" s="12" t="s">
         <v>214</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="F16" s="10" t="s">
+        <v>215</v>
       </c>
     </row>
   </sheetData>
@@ -3221,36 +3274,36 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
   </sheetData>
